--- a/results/mi355x_dsr_mxfp4/mi355x_dsr_mxfp4_mtp0_ep4_tp4_rocm711_profiling/prefill_breakdown.xlsx
+++ b/results/mi355x_dsr_mxfp4/mi355x_dsr_mxfp4_mtp0_ep4_tp4_rocm711_profiling/prefill_breakdown.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,132 +467,401 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>void aiter::reduce_scatter_cross_device_store&lt;std::bfloat16_t, 4&gt;(aiter::RankData*, aiter::RankSignals, aiter::Signal*, int, int)</t>
+          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 64, 8, false, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>155.12</v>
+        <v>4.439</v>
       </c>
       <c r="D2" t="n">
-        <v>65.40000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>169.479</v>
+        <v>4.439</v>
       </c>
       <c r="F2" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>183.578</v>
-      </c>
-      <c r="H2" t="n">
-        <v>196.4444878048781</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gemm_a16w16</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>void aiter::local_device_load_rmsnorm&lt;std::bfloat16_t, 512, 2&gt;(aiter::RankSignals, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, float, int, int, int)</t>
+          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT192x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT6_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA2_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.359</v>
+        <v>30.159</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12.86648780487805</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30.159</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>model.layers.20.self_attn.fused_qkv_a_proj</t>
+          <t>rope_cached_positions_2c_fwd_impl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+          <t>void aiter::kn_entry_2c_sbhd_cached_indirect_inplace&lt;aiter::OpCachedFwd, 1, true, false, true, true, c10::BFloat16, c10::BFloat16&gt;(c10::BFloat16*, c10::BFloat16*, c10::BFloat16 const*, c10::BFloat16 const*, long const*, int, int, int, int, int, int, int, int, int, int, int, int, int)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63.28</v>
+        <v>6.359</v>
       </c>
       <c r="D4" t="n">
-        <v>26.7</v>
+        <v>0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>63.28</v>
+        <v>6.359</v>
       </c>
       <c r="F4" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>62.50963414634146</v>
-      </c>
-      <c r="H4" t="n">
-        <v>62.50963414634146</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>post_attn_layernorm</t>
+          <t>kv_cache</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 256, 8, false, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
+          <t>void aiter::concat_and_cache_mla_opt_kernel&lt;std::bfloat16_t, _BitInt(8), (vllm::Fp8KVCacheDataType)1&gt;(std::bfloat16_t const*, std::bfloat16_t const*, _BitInt(8)*, long const*, int, int, int, int, int, int, int, float const*)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.559</v>
+        <v>4.519</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
-        <v>4.559</v>
+        <v>4.519</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.569756097560976</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.569756097560976</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>gemm_a16w16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR0_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR0_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20.919</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20.919</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>16.319</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.319</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FlashAttnVarlenFunc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aiter::fmha_fwd_hd192_hd128_bf16_causal_group</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gemm_a16w16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT224x256x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA128_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT7_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA1_VWB8_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>86.599</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>86.599</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>post_attn_layernorm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_copy__0</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8.679</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>410.36</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>void aiter::reduce_scatter_cross_device_store&lt;std::bfloat16_t, 4&gt;(aiter::RankData*, aiter::RankSignals, aiter::Signal*, int, int)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>388.362</v>
+      </c>
+      <c r="D11" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>void aiter::local_device_load_rmsnorm&lt;std::bfloat16_t, 512, 2&gt;(aiter::RankSignals, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, float, int, int, int)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13.319</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>model.layers.1.mlp.gate_up_proj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>void aiter::dynamic_per_group_scaled_quant_kernel&lt;std::bfloat16_t, opus::fp4_t, 32&gt;(opus::fp4_t*, float*, std::bfloat16_t const*, float const*, int, long, int, int, bool, int const*, int)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7.279</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>63.35899999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aiter::f4gemm_bf16_per1x32Fp4_BpreShuffle_64x768</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>silu_and_mul</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>void aiter::act_and_mul_kernel&lt;std::bfloat16_t, std::bfloat16_t, &amp;float aiter::silu_kernel&lt;std::bfloat16_t&gt;(std::bfloat16_t const&amp;), 8&gt;(std::bfloat16_t*, std::bfloat16_t const*, int)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>model.layers.1.mlp.down_proj</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>void aiter::dynamic_per_group_scaled_quant_kernel&lt;std::bfloat16_t, opus::fp4_t, 32&gt;(opus::fp4_t*, float*, std::bfloat16_t const*, float const*, int, long, int, int, bool, int const*, int)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5.199</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>43.958</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aiter::f4gemm_bf16_per1x32Fp4_BpreShuffle_64x768</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>38.759</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>237.318</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>722.0690000000001</v>
+      </c>
+      <c r="D18" t="n">
         <v>100</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
         <v>100</v>
       </c>
-      <c r="G6" t="n">
-        <v>263.5238780487805</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="H2:H3"/>
+  <mergeCells count="9">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -604,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,70 +913,260 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>155.12</v>
+        <v>388.362</v>
       </c>
       <c r="D2" t="n">
-        <v>155.12</v>
+        <v>388.362</v>
       </c>
       <c r="E2" t="n">
-        <v>65.40000000000001</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+          <t>aiter::f4gemm_bf16_per1x32Fp4_BpreShuffle_64x768</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.28</v>
+        <v>94.839</v>
       </c>
       <c r="D3" t="n">
-        <v>63.28</v>
+        <v>47.419</v>
       </c>
       <c r="E3" t="n">
-        <v>26.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>void aiter::local_device_load_rmsnorm&lt;std::bfloat16_t, 512, 2&gt;(aiter::RankSignals, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, float, int, int, int)</t>
+          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT224x256x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA128_LBSPPB1024_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT7_8_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA1_VWB8_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>14.359</v>
+        <v>86.599</v>
       </c>
       <c r="D4" t="n">
-        <v>14.359</v>
+        <v>86.599</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 256, 8, false, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
+          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT192x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT6_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA2_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>4.559</v>
+        <v>30.159</v>
       </c>
       <c r="D5" t="n">
-        <v>4.559</v>
+        <v>30.159</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aiter::fmha_fwd_hd192_hd128_bf16_causal_group</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_BBS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR0_CADS0_DTLA0_DTLB0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSU0_GSUAMB_GLS0_ISA950_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR0_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK3_SKXCCM8_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGRO0_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20.919</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20.919</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16.319</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16.319</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>void aiter::local_device_load_rmsnorm&lt;std::bfloat16_t, 512, 2&gt;(aiter::RankSignals, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, float, int, int, int)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>13.319</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13.319</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>void aiter::dynamic_per_group_scaled_quant_kernel&lt;std::bfloat16_t, opus::fp4_t, 32&gt;(opus::fp4_t*, float*, std::bfloat16_t const*, float const*, int, long, int, int, bool, int const*, int)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.478</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.239</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_copy__0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.679</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.679</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>void aiter::kn_entry_2c_sbhd_cached_indirect_inplace&lt;aiter::OpCachedFwd, 1, true, false, true, true, c10::BFloat16, c10::BFloat16&gt;(c10::BFloat16*, c10::BFloat16*, c10::BFloat16 const*, c10::BFloat16 const*, long const*, int, int, int, int, int, int, int, int, int, int, int, int, int)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>void aiter::act_and_mul_kernel&lt;std::bfloat16_t, std::bfloat16_t, &amp;float aiter::silu_kernel&lt;std::bfloat16_t&gt;(std::bfloat16_t const&amp;), 8&gt;(std::bfloat16_t*, std::bfloat16_t const*, int)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>void aiter::concat_and_cache_mla_opt_kernel&lt;std::bfloat16_t, _BitInt(8), (vllm::Fp8KVCacheDataType)1&gt;(std::bfloat16_t const*, std::bfloat16_t const*, _BitInt(8)*, long const*, int, int, int, int, int, int, int, float const*)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>void aiter::add_rmsnorm_quant_kernel&lt;std::bfloat16_t, std::bfloat16_t, 64, 8, false, false, true, 1&gt;(std::bfloat16_t*, std::bfloat16_t*, float*, std::bfloat16_t*, std::bfloat16_t*, std::bfloat16_t*, double, int, int, int, int, int, int, int, bool)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.439</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.439</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
